--- a/西笑院HP作業ログ_完全版.xlsx
+++ b/西笑院HP作業ログ_完全版.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +89,9 @@
     </font>
     <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -171,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +236,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -598,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2486,6 +2490,589 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>garden.jpegはルートに残存・未使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Googleセキュリティアラート説明：「ログインをブロックしました」（攻撃者によるGmail不正アクセス試行）・「パスワード漏洩」メールを調査。クロードコードとは無関係と確認。対策：パスワード変更・2段階認証（設定済み）</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>確認済</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>京都・山形からのログイン試行。Googleがブロック済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026/05/27</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bing Webmaster Tools 登録完了。index.htmlにBing認証メタタグ追加・GitHub push。sitemap.xml送信済み</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Google・Bing両方のSearch Console登録完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026/05/30</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cドライブ容量調査：クロードコード旧バージョン4つ（900MB）＋pipキャッシュ（160MB）削除。合計約1.06GB解放。Claude Desktop VMファイル（8.9GB）・WSL2（4.3GB）は保持</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>済</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cドライブ：220GBで63.5GB空き。問題なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>第9回作業セッション（2026-06-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>㊳</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Claude Code 再ログイン</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>APIセッションが期限切れでログアウト状態になっていた。/loginコマンドで再認証完了。原因：セッショントークンの有効期限切れ（定期的に再ログインが必要な仕様）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>サイト作業：なし（ログイン作業のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="inlineStr">
+        <is>
+          <t>帳簿追加機能（2026-06-27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>㊴</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>一覧印刷追加</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>一覧・検索タブに「一覧を印刷」ボタン。検索絞り込み結果をA4横向きで印刷</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>月次収入・支出別印刷</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>月次集計タブに「収入のみ印刷」「支出のみ印刷」ボタン追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>年次収入・支出別印刷</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>年次集計タブに「収入のみ印刷」「支出のみ印刷」ボタン追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>使い方更新</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3機能の説明を使い方タブに追記</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>㊶</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>台帳金額フィールド追加</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>付届け1回金額・墓地管理料金額を台帳モーダルに追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>台帳一覧表示更新</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>付届け列に「年4回・5,000円/回」、墓地管理料列に金額を表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>未収管理自動金額セット</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>支払済にするボタン押下時に台帳の金額を自動入力</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>カテゴリ並び替え刷新</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>アコーディオン折りたたみ＋ドラッグ&amp;ドロップに変更（↑↓ボタン廃止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>相手先フリガナ補完</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>漢字・フリガナ両方で予測変換対応（全フィールド）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026/08/29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>競合調査</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>泰岳寺（春日井市、taigakuji.net）調査・比較</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>既製テンプレート・多ページ構成。西笑院の優位点：デザインの独自性（家紋使用）、運用コスト（GitHub Pages無料 vs レンタルサーバー年1〜2万円）。泰岳寺の優位点：お知らせ更新頻度、住職個人の発信力（ブログ・SNS）。資料：泰岳寺HP調査比較資料_令和8年8月.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>サイト改善</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>お知らせ欄をnews.txtに外部化</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>泰岳寺調査の改善提案を踏まえ着手。index.html内の直書きから、news.txt（1行＝日付｜本文）をfetchして表示する方式に変更。代表者がHTMLタグを触らず行編集だけで更新可能に</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>サイト改善</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>お知らせ欄のアコーディオン化</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>4件目以降を「＋もっと見る」ボタンで開閉。FAQセクションと同じaria-expandedパターンを踏襲</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>コンテンツ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>年間行事に「当山施餓鬼会」（10月）を追加</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>近隣ご寺院より20名ほど僧侶を招き、先祖供養・三界万霊供養を行う法要である旨を記載</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>未コミットの画像削除を確認（要注意）</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>⚠️ 未対応</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>mineo-daikyu.jpg等、index.html参照中の画像がローカルで削除（未コミット）状態。峰尾大休/・境内案内掲載写真/フォルダに同内容が別途あり。本番未反映のため実害なしだが、今後のgit add -A等での誤コミットに注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>サイト改善</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>お知らせのフェード開閉・リンク対応・「随時」固定位置に対応</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>max-height+opacityでフェード演出。news.txt3項目目でリンク指定可能に。「随時」は件数制限対象外で常に最上部。追記は下に書くほど上に表示される仕様に変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>サイト改善</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>スマホでお知らせ本文が見切れる不具合を修正</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>max-height制限を6em→20emに拡大、768px以下で日付・本文を縦並びに変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>品質管理</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>/code-review(xhigh)でindex.html全体を精査、7件修正</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>画像パス切れ2件・お知らせ機能の自作バグ2件・問い合わせフォームのエラー無反応・ライトボックス矢印キー誤動作・モバイルメニュー二重表示を修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>緊急対応</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>峰尾大休老師の写真4枚が本番で一時的に表示されない事故</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>✅ 復旧済み</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>画像パス整理の際、移動先「峰尾大休/」フォルダがgit未登録だったことに気づかず参照だけ変更し一時的に破損。数分で発見・修正。教訓：パス変更前にgit ls-filesで移動先の登録有無を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>デザイン改修</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ヘッダーにLINEリンク・バッジ色・ロゴサイズを調整</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>競合HP（斟珠寺）を参考に、電話番号横にLINE公式アイコン（吹き出し型・緑・白文字LINE）を追加。「お気軽にご相談ください」はプレーンなゴールド文字。ロゴは元サイズと拡大版の中間で確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>デザイン改修</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>スマホ版メニューの電話番号を最下部に移動、LINEも追加</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>上部にあった電話番号表示をナビ最下部に移動し、「お気軽にご相談ください」＋電話番号・LINEを横並びで追加。折り返し不具合をフォントサイズ調整で解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>表記修正</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ヒーローにローマ字TOSOTSUZANを追加、フッターの誤記も修正</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>✅ 完了</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>「西笑院」の下・SEISHO-INの真上にTOSOTSUZANを追加。兜率天と同じ読みのためヘボン式はS1つが正式。フッターにあった「TOSSOTSUZAN」（S2つ）の誤記も統一</t>
         </is>
       </c>
     </row>
